--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Dinesh Agrawal</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9801172900</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9801172900</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1172,10 +1170,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -1186,7 +1182,7 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -544,18 +544,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -572,10 +590,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -612,7 +630,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>WiFi 6 Upgrade</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -628,7 +646,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,10 +701,15 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -677,8 +724,11 @@
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -692,6 +742,9 @@
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -716,7 +769,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -738,7 +791,7 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="41" customWidth="1" min="31" max="31"/>
+    <col width="45" customWidth="1" min="31" max="31"/>
     <col width="24" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
@@ -751,12 +804,12 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1216,6 +1269,214 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 9:44 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359687</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Rasmi Tamang</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Rasmi Tamang</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9705845954</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:44:02 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>CHB9849082193</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 05:04:04 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:44:02 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>27.71399, 85.38161, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>lnawami@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>02:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>1,9</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>16h 39m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -684,10 +684,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -732,19 +732,35 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -771,12 +787,12 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -786,19 +802,19 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="27" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="24" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1336,10 +1352,8 @@
           <t>Rasmi Tamang</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9705845954</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9705845954</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1429,10 +1443,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1443,37 +1455,245 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>16h 39m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 9:49 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358646</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Rp.Naan &amp; sekuwa house</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Rp.Naan &amp; sekuwa house</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9813537434</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:49:59 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>BKT9813537434</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:10:23 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:49:59 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Royal Ocean Cafe (ROC) - Restaurant M9F2+9FX Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>9813537434@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB393</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>16h 39m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 13h 39m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -546,7 +546,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -562,18 +562,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="B5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -634,10 +652,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -646,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -657,10 +675,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -669,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -684,13 +702,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,15 +720,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -722,45 +746,73 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>2</v>
+      <c r="E2" s="6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>3</v>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -774,18 +826,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -808,13 +860,13 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1556,10 +1608,8 @@
           <t>Rp.Naan &amp; sekuwa house</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9813537434</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9813537434</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1649,10 +1699,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1663,37 +1711,461 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 13h 39m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : Slow internet  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:09 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6 upgradation  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6 upgradation</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359619</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Angnima Sherpa</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Angnima Sherpa</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9818810378</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:09:26 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9818810378</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:19:10 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:09:26 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.71877</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Near Kushal Banquet, Boudhadwar Marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>angnimasherpa7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>03:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Gaurab Dahal</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L33-1</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.36044</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6 upgradation  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>1d 13h 39m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>17h 50m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : Slow internet  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6 upgradation  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:13 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>secondary router issue</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357881</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Rashik Rimal</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Rashik Rimal</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9840000161</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:13:06 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>LTP9802371497</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:55:22 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:13:06 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>ICIMOD Gate ICIMOD Gate - Non-profit organization J8WF+FR2 Lalitpur 44700, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>9802371497@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>10:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 17m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -872,7 +872,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1812,10 +1812,8 @@
           <t>Angnima Sherpa</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9818810378</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9818810378</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1850,10 +1848,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.71877</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.71877</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1909,25 +1905,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L33-1</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.36044</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.36044</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6 upgradation  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -2028,10 +2020,8 @@
           <t>Rashik Rimal</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9840000161</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9840000161</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2121,10 +2111,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2123,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : secondary router issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,25 +528,25 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -580,20 +580,74 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="B8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -652,14 +706,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -675,14 +729,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -702,14 +756,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -720,20 +777,35 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -749,19 +821,28 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>3</v>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -773,26 +854,44 @@
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -812,7 +911,16 @@
         <v>2</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -853,10 +961,10 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -870,12 +978,12 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -2157,6 +2265,1058 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:42 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359666</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Pun</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Pun</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9808567701</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:42:11 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9808567701</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:48:43 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:42:11 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>27.658872 85.316816, Near by Hope Collage - Lalitpur Metropolitan, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>03:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>17h 53m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:41 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Slow issue</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357830</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Gitaraj B.K</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Gitaraj B.K</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9823142863</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:37:17 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>CHB9823142863</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:29:40 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:41:01 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.69629624635759</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>ktm new road indrachowk, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>dtf5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Tika Kathayat</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>CDB392</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.32497406005861</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 3m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 11m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:38 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357783</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Singh Bhandari</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Singh Bhandari</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841047287</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:09:16 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841047287</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:09:16 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:38:32 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.698519</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Madan Bhandari Road, Kathmandu 44600,Near LAXMI AUTO PARTS, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>asatega2027@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.232391</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 29m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 29m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:38 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358398</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Prabodh Thapa</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Prabodh Thapa</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9844041672</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:38:49 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>KLK9844041672</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:19:44 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:38:49 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Danphe Colony - Housing development Q82M+R2J Danphe Colony Road Kathmandu 44600, Kathmandu, Nepal, N</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>thapaprabodh7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>10:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L12-3</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 19m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:34 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358216</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Durga Raj Gurung</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Durga Raj Gurung</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9851086658</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:34:31 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9851086658</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:41:24 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:34:31 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.731522</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Bajeko Sekuwa,P8J7+HRX, Samakhusi Marg, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>gurungkush99@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>10:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L26-3</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.314439</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 53m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -824,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -896,31 +896,59 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="F6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>10</v>
+      <c r="H6" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -934,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -968,7 +996,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -2332,10 +2360,8 @@
           <t>Bimala Pun</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9808567701</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9808567701</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2421,10 +2447,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -2435,7 +2459,7 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2536,10 +2560,8 @@
           <t>Gitaraj B.K</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9823142863</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9823142863</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2574,10 +2596,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.69629624635759</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.69629624635759</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2629,25 +2649,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>CDB392</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.32497406005861</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.32497406005861</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow issue  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2748,10 +2764,8 @@
           <t>Shyam Singh Bhandari</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841047287</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841047287</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2786,10 +2800,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.698519</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.698519</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2841,25 +2853,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.232391</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.23239100000001</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2960,10 +2968,8 @@
           <t>Prabodh Thapa</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9844041672</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9844041672</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -3053,10 +3059,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -3067,7 +3071,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3168,10 +3172,8 @@
           <t>Durga Raj Gurung</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9851086658</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9851086658</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3206,10 +3208,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.731522</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.731522</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3265,55 +3265,475 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L26-3</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.314439</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.31443899999999</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 53m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:47 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : low WiFi range  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>low WiFi range</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357627</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Hemata Bista</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Hemata Bista</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9767665971</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:47:43 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>CHB9767665971</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:54:06 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:47:43 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>NIST School Details from Google Maps Sano Thimi Marg, 16 Bhaktapur Rd, Madhyapur Thimi 44600, Bhakta</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>bistahemata50@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>10:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L5-5</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : low WiFi range  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>1d 18h 53m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 53m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : low WiFi range  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:49 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359328</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Sishir Lama</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Sishir Lama</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9860005605</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:49:07 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9860005605</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:57:28 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:49:07 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.72431</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Near Pashupati Dairy, Milijuli Chowk, Rayamajhi Marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>shishirtamang5555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>07:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>CDB064</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.31169</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>21h 51m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -870,14 +870,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -898,14 +898,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -924,31 +924,59 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>12</v>
+      <c r="H7" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX13"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1008,7 +1036,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3380,10 +3408,8 @@
           <t>Hemata Bista</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9767665971</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9767665971</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3473,10 +3499,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -3487,7 +3511,7 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : low WiFi range  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3588,10 +3612,8 @@
           <t>Sishir Lama</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9860005605</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9860005605</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3626,10 +3648,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.72431</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.72431</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3685,47 +3705,43 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>CDB064</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.31169</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.31169</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>21h 51m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>21h 51m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -3734,6 +3750,438 @@
       <c r="AX13" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:09 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:03 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:57 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr"/>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr"/>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="inlineStr"/>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:53 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr"/>
+      <c r="V17" s="3" t="inlineStr"/>
+      <c r="W17" s="3" t="inlineStr"/>
+      <c r="X17" s="3" t="inlineStr"/>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr"/>
+      <c r="AA17" s="3" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AC17" s="3" t="inlineStr"/>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr"/>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr"/>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr"/>
+      <c r="AM17" s="3" t="inlineStr"/>
+      <c r="AN17" s="3" t="inlineStr"/>
+      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4185,6 +4185,114 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:23 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr"/>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="3" t="inlineStr"/>
+      <c r="X18" s="3" t="inlineStr"/>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr"/>
+      <c r="AA18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr"/>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr"/>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr"/>
+      <c r="AM18" s="3" t="inlineStr"/>
+      <c r="AN18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>30.4%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -824,19 +824,19 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -964,19 +964,19 @@
         <v>2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1003,10 +1003,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="33" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1036,7 +1036,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4293,6 +4293,1262 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:37 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : umgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>umgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359368</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Dhaulagiri chinari guest house</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Reopen</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Dhaulagiri chinari guest house</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9840127065</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:43:38 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9851109196</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:25:23 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:37:22 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.731013</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>ranibari, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L35-2</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.310261</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : umgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>Negative Time</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>22h 11m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (Reopen)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : umgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:17 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358997</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Achut Baniya</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Achut Baniya</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9851245077</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:17:45 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9851245077</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:01:22 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:17:45 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Baniyatar Height Near of micro stand Kathmandu 44600, , ,</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>aonemotoparts@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>11:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L16-8</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:44 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357983</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>tika datta lamichane</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>tika datta lamichane</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9803539505</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:43:18 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803539505</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:43:18 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:44:03 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>chandragiri daha chwok , , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>11:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:43 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357983</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>tika datta lamichane</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>tika datta lamichane</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9803539505</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:43:18 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803539505</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:43:18 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:44:03 AM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>chandragiri daha chwok , , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>11:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:42 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357762</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Ram Hari Thapa Magar</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Ram Hari Thapa Magar</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9841639790</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:04:16 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9841639790</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:59:29 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:42:26 AM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.69455</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Thankot, Chandragiri ward no 3 near Mangoldaya Higher Secondary School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>11:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB013</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.22075</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 38m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:41 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357762</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Ram Hari Thapa Magar</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Ram Hari Thapa Magar</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9841639790</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:04:16 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9841639790</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:59:29 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:42:26 AM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.69455</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Thankot, Chandragiri ward no 3 near Mangoldaya Higher Secondary School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>11:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB013</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.22075</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 38m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>3</v>
@@ -976,7 +976,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AX28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4360,10 +4360,8 @@
           <t>Dhaulagiri chinari guest house</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9840127065</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9840127065</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4398,10 +4396,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.731013</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.731013</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4449,25 +4445,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>L35-2</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.310261</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.310261</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : umgrade wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4568,10 +4560,8 @@
           <t>Achut Baniya</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9851245077</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9851245077</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4661,10 +4651,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -4675,7 +4663,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4776,10 +4764,8 @@
           <t>tika datta lamichane</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9803539505</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9803539505</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4865,10 +4851,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4879,7 +4863,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4980,10 +4964,8 @@
           <t>tika datta lamichane</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9803539505</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9803539505</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5069,10 +5051,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -5083,7 +5063,7 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5184,10 +5164,8 @@
           <t>Ram Hari Thapa Magar</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9841639790</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9841639790</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5222,10 +5200,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.69455</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.69455</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5281,25 +5257,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>CDB013</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.22075</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.22075</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5400,10 +5372,8 @@
           <t>Ram Hari Thapa Magar</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9841639790</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9841639790</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5438,10 +5408,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.69455</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.69455</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5497,55 +5465,899 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB013</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.22075</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.22075</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 38m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 42m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 38m</t>
-        </is>
-      </c>
-      <c r="AT24" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 42m</t>
-        </is>
-      </c>
-      <c r="AU24" s="3" t="inlineStr">
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:52 AM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359787</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Vinod Ghiraiya</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Vinod Ghiraiya</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9851164008</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:52:11 AM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9851164008</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 06:41:51 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:52:11 AM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.68658</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Kupondole Kandevta complex ncc bank, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>vinodghiraiya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>03:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB598</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.31692</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>17h 10m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:49 AM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358886</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Upendra khatri</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Upendra khatri</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851069228</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:49:45 AM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851069228</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:18:35 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:49:45 AM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Him Rashmi High School/ College - Middle school Kathmandu Tarakeshwar 09, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>upendra_missu@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>11:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L35-4</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 31m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Payment collection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Payment collection</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352505</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Shrestha</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Shrestha</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9841217366</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:49:45 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9841217366</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:02:17 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:50:28 AM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.71041</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Near Bajra Hotel, Dallu , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>01:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>CDB254</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.30227</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Payment collection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>5d 23h 48m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW24" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX24" s="3" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Payment collection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:49 AM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Payment collection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Payment collection</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352505</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Shrestha</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Shrestha</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9841217366</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:49:45 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9841217366</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:02:17 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:50:28 AM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>27.71041</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Near Bajra Hotel, Dallu , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>01:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>CDB254</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>85.30227</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Payment collection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>5d 23h 48m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Payment collection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.1%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX28"/>
+  <dimension ref="A1:AX29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5580,10 +5580,8 @@
           <t>Vinod Ghiraiya</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9851164008</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9851164008</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5618,10 +5616,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.68658</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.68658</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5677,25 +5673,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB598</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.31692</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.31692</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5796,10 +5788,8 @@
           <t>Upendra khatri</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851069228</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851069228</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5889,10 +5879,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
@@ -5903,7 +5891,7 @@
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -6004,10 +5992,8 @@
           <t>Sunil Shrestha</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9841217366</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9841217366</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6042,10 +6028,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.71041</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.71041</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -6097,25 +6081,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>CDB254</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.30227</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.30226999999999</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : Payment collection  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6216,10 +6196,8 @@
           <t>Sunil Shrestha</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9841217366</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9841217366</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6254,10 +6232,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>27.71041</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>27.71041</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -6309,47 +6285,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>CDB254</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>85.30227</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>85.30226999999999</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>5d 23h 48m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
           <t>Case : Payment collection  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>1d 18h</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>5d 23h 48m</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV28" s="3" t="inlineStr">
-        <is>
-          <t>Case : Payment collection  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -6358,6 +6330,218 @@
       <c r="AX28" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:02 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : umgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>umgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359368</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Dhaulagiri chinari guest house</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Dhaulagiri chinari guest house</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9840127065</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:43:38 AM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9851109196</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:25:23 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:02:01 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.731013</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>ranibari, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>08:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>L35-2</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.310261</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : umgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>18m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>22h 36m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : umgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX29"/>
+  <dimension ref="A1:AX31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1036,7 +1036,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6400,10 +6400,8 @@
           <t>Dhaulagiri chinari guest house</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9840127065</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9840127065</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6438,10 +6436,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.731013</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.731013</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6493,47 +6489,43 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>L35-2</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.310261</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.310261</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>18m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>22h 36m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
           <t>Case : umgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>18m</t>
-        </is>
-      </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>22h 36m</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV29" s="3" t="inlineStr">
-        <is>
-          <t>Case : umgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -6542,6 +6534,222 @@
       <c r="AX29" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:18 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr"/>
+      <c r="V30" s="3" t="inlineStr"/>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr"/>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr"/>
+      <c r="AA30" s="3" t="inlineStr"/>
+      <c r="AB30" s="3" t="inlineStr"/>
+      <c r="AC30" s="3" t="inlineStr"/>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr"/>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr"/>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr"/>
+      <c r="AM30" s="3" t="inlineStr"/>
+      <c r="AN30" s="3" t="inlineStr"/>
+      <c r="AO30" s="3" t="inlineStr"/>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:17 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr"/>
+      <c r="V31" s="3" t="inlineStr"/>
+      <c r="W31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="inlineStr"/>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr"/>
+      <c r="AA31" s="3" t="inlineStr"/>
+      <c r="AB31" s="3" t="inlineStr"/>
+      <c r="AC31" s="3" t="inlineStr"/>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr"/>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr"/>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr"/>
+      <c r="AM31" s="3" t="inlineStr"/>
+      <c r="AN31" s="3" t="inlineStr"/>
+      <c r="AO31" s="3" t="inlineStr"/>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>4</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>4</v>
@@ -976,7 +976,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX31"/>
+  <dimension ref="A1:AX32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1036,7 +1036,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6753,6 +6753,222 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:37 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet issue</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358121</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Bhola Gurung</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Bhola Gurung</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9823807732</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:37:55 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9818990717</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:52:45 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:37:55 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.765437</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Pasikot, Budhanilkantha 04, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>bholagrg83@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>12:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Aayesha Maharjan</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L51-7</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.347144</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 45m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>30.3%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -967,7 +967,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>3</v>
@@ -976,7 +976,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AX34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6820,10 +6820,8 @@
           <t>Bhola Gurung</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9823807732</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9823807732</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6858,10 +6856,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.765437</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.765437</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6917,55 +6913,463 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L51-7</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.347144</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.347144</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 45m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : Slow internet issue  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359000</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Chem Pun</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Chem Pun</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9851273125</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:53:55 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851273125</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:03:57 AM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:53:55 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>TEJASWI ACADEMY - School Q877+8VG Tarakeshwar 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>9851273125@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>12:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Maharjan</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>L49-1</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>1d 21h 45m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 49m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : Slow internet issue  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW32" s="3" t="inlineStr">
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358952</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9840877910</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX32" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:52:32 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9840877910</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:20:16 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:52:32 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Q856+RH2 Road Tarakeshwar 44600,Q856+RH2 Road Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>dangolsanjay292@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 32m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -833,10 +833,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -961,7 +961,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>6</v>
@@ -973,10 +973,10 @@
         <v>3</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX34"/>
+  <dimension ref="A1:AX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1024,7 +1024,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -7028,10 +7028,8 @@
           <t>Chem Pun</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9851273125</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9851273125</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7121,10 +7119,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -7135,7 +7131,7 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7236,10 +7232,8 @@
           <t>Sanjay Dangol</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9840877910</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9840877910</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7325,10 +7319,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -7339,37 +7331,461 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 32m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 1:04 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358340</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Kumar Maharjan</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Kumar Maharjan</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9863589830</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:04:33 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>KLK9863589830</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:49:45 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:04:33 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>ktm soyambhu, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>kumar85@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>13:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 32m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 14m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX34" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358933</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Algorithm incorporate pvt.ltd</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Algorithm incorporate pvt.ltd</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9862382848</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:04:10 AM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9862382848</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:04:10 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:16:24 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.730899</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>27.73140206139827, 85.28583730005533, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>manishghimire153200@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>13:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>CDB508</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.285978</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 12m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 12m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -898,17 +898,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -926,17 +926,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -952,31 +952,59 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="4" t="n">
+      <c r="D8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="4" t="n">
-        <v>25</v>
+      <c r="G8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX36"/>
+  <dimension ref="A1:AX40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1001,14 +1029,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="31" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="33" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="33" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -1018,7 +1046,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -1039,7 +1067,7 @@
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -7432,10 +7460,8 @@
           <t>Kumar Maharjan</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9863589830</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9863589830</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7525,10 +7551,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -7539,7 +7563,7 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7640,10 +7664,8 @@
           <t>Algorithm incorporate pvt.ltd</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9862382848</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9862382848</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7678,10 +7700,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.730899</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.730899</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7737,47 +7757,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>CDB508</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.285978</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.285978</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 12m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 12m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 12m</t>
-        </is>
-      </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 12m</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV36" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -7786,6 +7802,834 @@
       <c r="AX36" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 1:19 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359444</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Mahat Pandey</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Mahat Pandey</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9841920384</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:20:35 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841920384</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:10:37 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:20:35 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Agraj Group Industries Pvt. Ltd - Mineral water company P8W8+G5F Sayapatri Nagar Tokha municipality</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>9841920384@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr"/>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Tika Kathayat</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>23h 9m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 1:24 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>frequent disconnection issue</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360191</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Jaisilal pandit</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Jaisilal pandit</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9821261736</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:24:08 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>KLK9821261736</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 08:55:12 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:24:08 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Hattigauda, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>9821261736@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Due to Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>03:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>4h 28m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 1:20 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358197</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Surendra Prakash Manandhar</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Surendra Prakash Manandhar</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9851050478</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:20:35 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851050478</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:34:51 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:20:35 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Kuleshwor Ganeshthan Temple - Hindu temple M7RX+2R3 University Path Kathmandu 44600, Bagmati, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>9851050478@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>13:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>CDB318</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 45m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 1:17 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : router exchange  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358197</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Surendra Prakash Manandhar</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Surendra Prakash Manandhar</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9851050478</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:20:35 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851050478</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:34:51 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:20:35 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Kuleshwor Ganeshthan Temple - Hindu temple M7RX+2R3 University Path Kathmandu 44600, Bagmati, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>9851050478@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>13:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>CDB318</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : router exchange  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 45m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : router exchange  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -1064,7 +1064,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7872,10 +7872,8 @@
           <t>Laxmi Mahat Pandey</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9841920384</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9841920384</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7961,10 +7959,8 @@
           <t>Tika Kathayat</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -7975,7 +7971,7 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -8076,10 +8072,8 @@
           <t>Jaisilal pandit</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9821261736</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9821261736</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8169,10 +8163,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
@@ -8183,7 +8175,7 @@
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -8284,10 +8276,8 @@
           <t>Surendra Prakash Manandhar</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9851050478</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9851050478</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8377,10 +8367,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -8391,7 +8379,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -8492,10 +8480,8 @@
           <t>Surendra Prakash Manandhar</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9851050478</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9851050478</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8585,10 +8571,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
@@ -8599,7 +8583,7 @@
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : router exchange  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -870,7 +870,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -880,13 +880,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -898,7 +898,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -926,14 +926,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -954,17 +954,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -980,31 +980,59 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>28</v>
+      <c r="H9" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1018,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX40"/>
+  <dimension ref="A1:AX42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1047,7 +1075,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -1064,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8617,6 +8645,430 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  internet     has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>no  internet</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350793</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Sonim Manandhar</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Sonim Manandhar</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9702616130</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:49:09 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>KLK9702616130</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:48:46 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:57:44 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Chamati Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>9702616130@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>15:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB313</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr"/>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  internet     has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 8m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>7d 16h 8m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  internet     has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 1:56 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  internet     has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>no  internet</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350793</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Sonim Manandhar</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Sonim Manandhar</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9702616130</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:49:09 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>KLK9702616130</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:48:46 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:57:44 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Chamati Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>9702616130@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>15:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>CDB313</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  internet     has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 8m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>7d 16h 8m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  internet     has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -1092,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8712,10 +8712,8 @@
           <t>Sonim Manandhar</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9702616130</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9702616130</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8787,10 +8785,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH41" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH41" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
@@ -8809,10 +8805,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
@@ -8823,7 +8817,7 @@
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : no  internet     has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8924,10 +8918,8 @@
           <t>Sonim Manandhar</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9702616130</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9702616130</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8999,10 +8991,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH42" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
@@ -9021,10 +9011,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
@@ -9035,7 +9023,7 @@
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : no  internet     has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>69.6%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>30.4%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>52.2%</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -830,13 +830,13 @@
         <v>7</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -1017,7 +1017,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>7</v>
@@ -1026,13 +1026,13 @@
         <v>7</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX42"/>
+  <dimension ref="A1:AX47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1092,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9057,6 +9057,958 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358379</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Melina Rai</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Melina Rai</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9813553277</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:10:33 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>CHB9813553277</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:10:33 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:26:21 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Maru Hiti Maru Hiti - Drinking water Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>raimelina251@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr"/>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>CDB282</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr"/>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 15m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 15m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358347</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Supa Deurali Security Service</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Supa Deurali Security Service</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9851172051</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:07:38 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9808787334</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:51:08 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:07:38 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Suichatar Sahid memorial hospital, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>sds.kathmandu14@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>14:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>CDB352</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 16m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:08 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358246</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Piyush Thakur</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Piyush Thakur</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9818289890</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:08:01 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9818289890</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:54:13 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:08:01 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.69838</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>near by Diamond Banquet &amp; Events - Banquet hall P72P+6J4 Bafal Marg Kathmandu 44600, Bagmati, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>tpiyush531@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>14:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>CDB086</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.284</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 13m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:23 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi  6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi  6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359143</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Baniya</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Baniya</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9762450263</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:15:53 AM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9762450263</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:15:53 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:23:55 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.72838</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Nearkharibot banasthali Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>sujanbaniya96@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>13:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>CDB476</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.292696</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi  6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 8m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 8m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi  6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:14 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr"/>
+      <c r="W47" s="3" t="inlineStr"/>
+      <c r="X47" s="3" t="inlineStr"/>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr"/>
+      <c r="AA47" s="3" t="inlineStr"/>
+      <c r="AB47" s="3" t="inlineStr"/>
+      <c r="AC47" s="3" t="inlineStr"/>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr"/>
+      <c r="AF47" s="3" t="inlineStr"/>
+      <c r="AG47" s="3" t="inlineStr"/>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr"/>
+      <c r="AM47" s="3" t="inlineStr"/>
+      <c r="AN47" s="3" t="inlineStr"/>
+      <c r="AO47" s="3" t="inlineStr"/>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -1092,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9124,10 +9124,8 @@
           <t>Melina Rai</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9813553277</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9813553277</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9213,10 +9211,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
@@ -9227,7 +9223,7 @@
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -9318,20 +9314,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Supa Deurali Security Service</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9851172051</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9851172051</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9421,10 +9411,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
@@ -9435,7 +9423,7 @@
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9536,10 +9524,8 @@
           <t>Piyush Thakur</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9818289890</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9818289890</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9574,10 +9560,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.69838</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.69838</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9633,25 +9617,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>CDB086</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.284</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.28400000000001</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -9752,10 +9732,8 @@
           <t>Sujan Baniya</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9762450263</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9762450263</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9790,10 +9768,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.72838</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.72838</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -9849,25 +9825,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>CDB476</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.292696</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.29269600000001</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi  6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>32.7%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5</v>
@@ -830,13 +830,13 @@
         <v>7</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>6</v>
@@ -1026,13 +1026,13 @@
         <v>7</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX47"/>
+  <dimension ref="A1:AX50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1092,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9981,6 +9981,654 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:42 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358321</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Shambhu Raj Acharya</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Shambhu Raj Acharya</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9851159441</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:42:51 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9851159441</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:38:38 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:42:51 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.69349</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Near Ganeshsthan, Tripura Marg, Kathmandu 44600 , Near ????????????? ????????, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>shambhuacharya79@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>14:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>.85.3144</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 4m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:39 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357880</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Roshani Maharjan</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Roshani Maharjan</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9841757094</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:55:21 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9841757094</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:55:21 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:39:00 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.717138</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu 44600 Near by National College NIST, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>roshani2037@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>14:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>CDB475</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.303544</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 43m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 43m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:38 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357880</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Roshani Maharjan</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Roshani Maharjan</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9841757094</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:55:21 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9841757094</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:55:21 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:39:00 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.717138</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu 44600 Near by National College NIST, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>roshani2037@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>14:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>CDB475</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.303544</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 43m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 43m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>31.4%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX50"/>
+  <dimension ref="A1:AX52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10048,10 +10048,8 @@
           <t>Shambhu Raj Acharya</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9851159441</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9851159441</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10086,10 +10084,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.69349</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.69349</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -10145,10 +10141,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
@@ -10163,7 +10157,7 @@
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
@@ -10264,10 +10258,8 @@
           <t>Roshani Maharjan</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9841757094</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9841757094</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10302,10 +10294,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.717138</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.717138</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -10361,10 +10351,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
@@ -10379,7 +10367,7 @@
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -10480,10 +10468,8 @@
           <t>Roshani Maharjan</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9841757094</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9841757094</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10518,10 +10504,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.717138</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.717138</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -10577,10 +10561,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
@@ -10595,37 +10577,469 @@
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 43m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 43m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS50" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 43m</t>
-        </is>
-      </c>
-      <c r="AT50" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 43m</t>
-        </is>
-      </c>
-      <c r="AU50" s="3" t="inlineStr">
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:52 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357783</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Singh Bhandari</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Singh Bhandari</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9841047287</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:09:16 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9841047287</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:09:16 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:52:20 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.698519</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Madan Bhandari Road, Kathmandu 44600,Near LAXMI AUTO PARTS, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>asatega2027@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>14:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.232391</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 43m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 43m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV50" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW50" s="3" t="inlineStr">
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:51 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357783</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Singh Bhandari</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Singh Bhandari</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9841047287</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX50" s="3" t="inlineStr">
-        <is>
-          <t>Ajit Shrestha</t>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:09:16 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9841047287</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:09:16 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:52:20 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.698519</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Madan Bhandari Road, Kathmandu 44600,Near LAXMI AUTO PARTS, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>asatega2027@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>14:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.232391</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 43m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 43m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -706,42 +706,65 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>85.2%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>52.9%</t>
+      <c r="B4" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>82.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>50.9%</t>
         </is>
       </c>
     </row>
@@ -821,7 +844,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -830,23 +853,23 @@
         <v>7</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -858,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -870,29 +893,29 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Due to Configuration Issue</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -954,17 +977,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Due to Configuration Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -1014,10 +1037,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>7</v>
@@ -1026,13 +1049,13 @@
         <v>7</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX52"/>
+  <dimension ref="A1:AX58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10678,10 +10701,8 @@
           <t>Shyam Singh Bhandari</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9841047287</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9841047287</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10716,10 +10737,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.698519</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.698519</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -10775,10 +10794,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -10793,7 +10810,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -10894,10 +10911,8 @@
           <t>Shyam Singh Bhandari</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9841047287</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9841047287</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10932,10 +10947,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.698519</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.698519</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10991,10 +11004,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
@@ -11009,37 +11020,1297 @@
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 43m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 43m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS52" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 43m</t>
-        </is>
-      </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 43m</t>
-        </is>
-      </c>
-      <c r="AU52" s="3" t="inlineStr">
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 3:25 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358334</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Sita Devi Maharjan</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Sita Devi Maharjan</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9841733174</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:25:47 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9803146411</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:47:41 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:25:47 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr"/>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Near Bagh Bhairab Temple Details from Google Maps Chithu Marg, Kirtipur 44600, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>krish3heetrip@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>15:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr"/>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 38m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 3:27 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter  Faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Router / Adapter  Faulty</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359548</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Chaudhary</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Chaudhary</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9762969561</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:39:40 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9762969561</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:30:33 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:27:02 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki	Kalimati, karakhusi Marg	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr"/>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>09:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter  Faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>23h 47m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>23h 56m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV52" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW52" s="3" t="inlineStr">
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter  Faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 3:26 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter  Faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Router / Adapter  Faulty</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359548</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Chaudhary</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Chaudhary</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9762969561</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:39:40 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9762969561</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:30:33 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:27:02 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr"/>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki	Kalimati, karakhusi Marg	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr"/>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>09:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr"/>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter  Faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>23h 47m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>23h 56m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter  Faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 3:14 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358237</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Alok Tuladhar</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Alok Tuladhar</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9851012482</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:49:21 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9851012482</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:49:21 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:14:33 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.707538</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>P845+VP4, Yogbir Singh Marg, Kathmandu 44600 Near by Rato Hatti Ganesh Mandir, , ,</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>alokstuladhar@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr"/>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>4,2</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.309516</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 25m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 25m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 3:05 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358237</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Alok Tuladhar</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Alok Tuladhar</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9851012482</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:49:21 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9851012482</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:49:21 PM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:14:33 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.707538</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>P845+VP4, Yogbir Singh Marg, Kathmandu 44600 Near by Rato Hatti Ganesh Mandir, , ,</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>alokstuladhar@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr"/>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>4,2</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.309516</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 25m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 25m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 2:56 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358898</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Pankaj Karnami</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Pankaj Karnami</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9808363062</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:30:04 AM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>9808363062</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:30:04 AM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:56:21 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr">
+        <is>
+          <t>27.697944</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>M8X5+8QH, Sungabha Marg, Kathmandu 44600 Near by Bhotebahal Plaza, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>pkarnami123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr"/>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>85.310046</t>
+        </is>
+      </c>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 26m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 26m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX52" s="3" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
+      <c r="AX58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11121,10 +11121,8 @@
           <t>Sita Devi Maharjan</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9841733174</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9841733174</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -11214,10 +11212,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
@@ -11228,7 +11224,7 @@
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -11329,10 +11325,8 @@
           <t>Bikash Chaudhary</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9762969561</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9762969561</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -11400,10 +11394,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH54" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH54" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI54" s="3" t="inlineStr">
         <is>
@@ -11422,10 +11414,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -11436,7 +11426,7 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : Router / Adapter  Faulty   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -11537,10 +11527,8 @@
           <t>Bikash Chaudhary</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9762969561</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9762969561</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11608,10 +11596,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH55" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH55" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI55" s="3" t="inlineStr">
         <is>
@@ -11630,10 +11616,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
@@ -11644,7 +11628,7 @@
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : Router / Adapter  Faulty   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -11745,10 +11729,8 @@
           <t>Alok Tuladhar</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9851012482</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9851012482</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11783,10 +11765,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.707538</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.707538</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -11838,10 +11818,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
@@ -11856,7 +11834,7 @@
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
@@ -11957,10 +11935,8 @@
           <t>Alok Tuladhar</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9851012482</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9851012482</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -11995,10 +11971,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.707538</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.707538</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -12050,10 +12024,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
@@ -12068,7 +12040,7 @@
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
@@ -12169,10 +12141,8 @@
           <t>Pankaj Karnami</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9808363062</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9808363062</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -12207,10 +12177,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y58" s="3" t="inlineStr">
-        <is>
-          <t>27.697944</t>
-        </is>
+      <c r="Y58" s="3" t="n">
+        <v>27.697944</v>
       </c>
       <c r="Z58" s="3" t="inlineStr">
         <is>
@@ -12262,10 +12230,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
@@ -12280,7 +12246,7 @@
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.5%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -856,10 +856,10 @@
         <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -1052,10 +1052,10 @@
         <v>7</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX58"/>
+  <dimension ref="A1:AX59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12280,6 +12280,222 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359699</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Sangharsha phuyal</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Sangharsha phuyal</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9803256384</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 05:16:50 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9803256384</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 05:16:50 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:47:40 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.69673</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Near New Diamond Academy, M7V9+R3Q, Melissa Marga, Chandragiri, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>sangharshaf@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>08:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>CDB604</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.2663</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>22h 30m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>22h 30m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7</v>
@@ -859,7 +859,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>8</v>
@@ -1055,7 +1055,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX59"/>
+  <dimension ref="A1:AX61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12347,10 +12347,8 @@
           <t>Sangharsha phuyal</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9803256384</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9803256384</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -12385,10 +12383,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>27.69673</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>27.69673</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -12444,10 +12440,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
@@ -12462,29 +12456,29 @@
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>22h 30m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>22h 30m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS59" s="3" t="inlineStr">
-        <is>
-          <t>22h 30m</t>
-        </is>
-      </c>
-      <c r="AT59" s="3" t="inlineStr">
-        <is>
-          <t>22h 30m</t>
-        </is>
-      </c>
-      <c r="AU59" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV59" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW59" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -12493,6 +12487,438 @@
       <c r="AX59" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 4:11 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358131</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Aura Home</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Aura Home</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9840788764</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:58:51 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9840788764</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:58:51 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:11:17 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>27.69269</t>
+        </is>
+      </c>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>Kuleshwore car vatika, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>riyeshshrestha1094@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>16:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>85.29731</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 4:10 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358131</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Aura Home</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Aura Home</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9840788764</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:58:51 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>9840788764</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:58:51 PM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:11:17 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr">
+        <is>
+          <t>27.69269</t>
+        </is>
+      </c>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>Kuleshwore car vatika, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr">
+        <is>
+          <t>riyeshshrestha1094@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr"/>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>16:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr">
+        <is>
+          <t>85.29731</t>
+        </is>
+      </c>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 12m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12557,10 +12557,8 @@
           <t>Aura Home</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9840788764</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9840788764</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -12595,10 +12593,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y60" s="3" t="inlineStr">
-        <is>
-          <t>27.69269</t>
-        </is>
+      <c r="Y60" s="3" t="n">
+        <v>27.69269</v>
       </c>
       <c r="Z60" s="3" t="inlineStr">
         <is>
@@ -12654,10 +12650,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
@@ -12672,7 +12666,7 @@
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
@@ -12773,10 +12767,8 @@
           <t>Aura Home</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9840788764</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9840788764</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -12811,10 +12803,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y61" s="3" t="inlineStr">
-        <is>
-          <t>27.69269</t>
-        </is>
+      <c r="Y61" s="3" t="n">
+        <v>27.69269</v>
       </c>
       <c r="Z61" s="3" t="inlineStr">
         <is>
@@ -12870,10 +12860,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
@@ -12888,7 +12876,7 @@
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>43</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>70.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.8%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.6%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>26</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.5%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -859,7 +859,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -1040,7 +1040,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>7</v>
@@ -1055,7 +1055,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX61"/>
+  <dimension ref="A1:AX62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12910,6 +12910,218 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 5:05 PM</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359965</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Sita Bhattarai</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Sita Bhattarai</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>9808621260</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:09:50 PM</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>9808621260</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:09:50 PM</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 05:05:55 PM</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="inlineStr">
+        <is>
+          <t>27.64685</t>
+        </is>
+      </c>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA62" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB62" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC62" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr">
+        <is>
+          <t>Nakhipot, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF62" s="3" t="inlineStr">
+        <is>
+          <t>siteydesigns@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="inlineStr"/>
+      <c r="AI62" s="3" t="inlineStr"/>
+      <c r="AJ62" s="3" t="inlineStr"/>
+      <c r="AK62" s="3" t="inlineStr"/>
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr">
+        <is>
+          <t>85.31508</t>
+        </is>
+      </c>
+      <c r="AQ62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>19h 56m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>19h 56m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX62" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>43</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>26</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>8</v>
@@ -859,7 +859,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>9</v>
@@ -1055,7 +1055,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX62"/>
+  <dimension ref="A1:AX63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12977,10 +12977,8 @@
           <t>Sita Bhattarai</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>9808621260</t>
-        </is>
+      <c r="O62" s="3" t="n">
+        <v>9808621260</v>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
@@ -13015,10 +13013,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y62" s="3" t="inlineStr">
-        <is>
-          <t>27.64685</t>
-        </is>
+      <c r="Y62" s="3" t="n">
+        <v>27.64685</v>
       </c>
       <c r="Z62" s="3" t="inlineStr">
         <is>
@@ -13070,10 +13066,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN62" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
@@ -13088,37 +13082,249 @@
       <c r="AQ62" s="3" t="inlineStr"/>
       <c r="AR62" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>19h 56m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>19h 56m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS62" s="3" t="inlineStr">
-        <is>
-          <t>19h 56m</t>
-        </is>
-      </c>
-      <c r="AT62" s="3" t="inlineStr">
-        <is>
-          <t>19h 56m</t>
-        </is>
-      </c>
-      <c r="AU62" s="3" t="inlineStr">
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX62" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 5:30 PM</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357832</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Ram Bijay Yadav</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Ram Bijay Yadav</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>9841821402</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:30:36 PM</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>9841821402</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:30:36 PM</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 05:30:30 PM</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr">
+        <is>
+          <t>27.70173</t>
+        </is>
+      </c>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>putalisadak near raktakali driving centre, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr">
+        <is>
+          <t>ramyadav2065@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr"/>
+      <c r="AI63" s="3" t="inlineStr"/>
+      <c r="AJ63" s="3" t="inlineStr"/>
+      <c r="AK63" s="3" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>CDB282</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr">
+        <is>
+          <t>85.323</t>
+        </is>
+      </c>
+      <c r="AQ63" s="3" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV62" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW62" s="3" t="inlineStr">
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX62" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX63" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.8%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -856,10 +856,10 @@
         <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -1052,10 +1052,10 @@
         <v>7</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX63"/>
+  <dimension ref="A1:AX64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -13183,10 +13183,8 @@
           <t>Ram Bijay Yadav</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>9841821402</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>9841821402</v>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -13221,10 +13219,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y63" s="3" t="inlineStr">
-        <is>
-          <t>27.70173</t>
-        </is>
+      <c r="Y63" s="3" t="n">
+        <v>27.70173</v>
       </c>
       <c r="Z63" s="3" t="inlineStr">
         <is>
@@ -13276,10 +13272,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN63" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
@@ -13294,29 +13288,29 @@
       <c r="AQ63" s="3" t="inlineStr"/>
       <c r="AR63" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS63" s="3" t="inlineStr">
-        <is>
-          <t>2d 4h 59m</t>
-        </is>
-      </c>
-      <c r="AT63" s="3" t="inlineStr">
-        <is>
-          <t>2d 4h 59m</t>
-        </is>
-      </c>
-      <c r="AU63" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV63" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW63" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -13325,6 +13319,222 @@
       <c r="AX63" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 5:32 PM</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359288</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Sweety Manandhar</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Sweety Manandhar</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>9860029357</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:32:38 PM</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>9860029357</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:32:38 PM</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 05:32:33 PM</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>27.688531</t>
+        </is>
+      </c>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>Check Post Near Himal Enterprises , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr">
+        <is>
+          <t>sweetymanandhar7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr"/>
+      <c r="AI64" s="3" t="inlineStr">
+        <is>
+          <t>15:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ64" s="3" t="inlineStr"/>
+      <c r="AK64" s="3" t="inlineStr"/>
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>CDB424</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>85.232134</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr"/>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX64" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13389,10 +13389,8 @@
           <t>Sweety Manandhar</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>9860029357</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>9860029357</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -13427,10 +13425,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y64" s="3" t="inlineStr">
-        <is>
-          <t>27.688531</t>
-        </is>
+      <c r="Y64" s="3" t="n">
+        <v>27.688531</v>
       </c>
       <c r="Z64" s="3" t="inlineStr">
         <is>
@@ -13486,10 +13482,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN64" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
@@ -13504,7 +13498,7 @@
       <c r="AQ64" s="3" t="inlineStr"/>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.8%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -859,7 +859,7 @@
         <v>7</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -1040,7 +1040,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>7</v>
@@ -1055,7 +1055,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX64"/>
+  <dimension ref="A1:AX65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13532,6 +13532,226 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 6:27 PM</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360542</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Pravin Chaudhary</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>Pravin Chaudhary</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>9841918849</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 06:27:21 PM</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>9841918849</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:38:00 PM</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 06:27:21 PM</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr">
+        <is>
+          <t>27.65877</t>
+        </is>
+      </c>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>Near Nirmal School, Nakhu, Manjushree marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr">
+        <is>
+          <t>Prancechaudhary111@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI65" s="3" t="inlineStr">
+        <is>
+          <t>05:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ65" s="3" t="inlineStr"/>
+      <c r="AK65" s="3" t="inlineStr"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr">
+        <is>
+          <t>85.29796</t>
+        </is>
+      </c>
+      <c r="AQ65" s="3" t="inlineStr"/>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>5h 49m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX65" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_06_Oct_2026.xlsx
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13599,10 +13599,8 @@
           <t>Pravin Chaudhary</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>9841918849</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>9841918849</v>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -13637,10 +13635,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y65" s="3" t="inlineStr">
-        <is>
-          <t>27.65877</t>
-        </is>
+      <c r="Y65" s="3" t="n">
+        <v>27.65877</v>
       </c>
       <c r="Z65" s="3" t="inlineStr">
         <is>
@@ -13678,10 +13674,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH65" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH65" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI65" s="3" t="inlineStr">
         <is>
@@ -13700,10 +13694,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN65" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
@@ -13718,7 +13710,7 @@
       <c r="AQ65" s="3" t="inlineStr"/>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
